--- a/artfynd/A 21214-2023 artfynd.xlsx
+++ b/artfynd/A 21214-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY8"/>
+  <dimension ref="A1:AY22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1412,6 +1412,1434 @@
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>120542164</v>
+      </c>
+      <c r="B9" t="n">
+        <v>100194</v>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Isgärde, Öl</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>594894</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6290481</v>
+      </c>
+      <c r="S9" t="n">
+        <v>10</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Mörbylånga</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Öland</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Glömminge</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2024-10-14</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2024-10-14</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Patrik Celander</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Patrik Celander</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>120542979</v>
+      </c>
+      <c r="B10" t="n">
+        <v>110061</v>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>219711</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Sårläka</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Sanicula europaea</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Isgärde, Öl</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>595162</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6290464</v>
+      </c>
+      <c r="S10" t="n">
+        <v>10</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Mörbylånga</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Öland</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Glömminge</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2024-10-16</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2024-10-16</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Patrik Celander</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Patrik Celander, Örjan Fritz</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>120542154</v>
+      </c>
+      <c r="B11" t="n">
+        <v>8346</v>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>106540</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Svart askbastborre</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Hylesinus crenatus</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(Fabricius, 1787)</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Isgärde, Öl</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>595044</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6290419</v>
+      </c>
+      <c r="S11" t="n">
+        <v>10</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Mörbylånga</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Öland</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Glömminge</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2024-10-14</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2024-10-14</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Patrik Celander</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Patrik Celander</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>120542161</v>
+      </c>
+      <c r="B12" t="n">
+        <v>8432</v>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>106545</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Mindre märgborre</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Tomicus minor</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Isgärde, Öl</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>595077</v>
+      </c>
+      <c r="R12" t="n">
+        <v>6290472</v>
+      </c>
+      <c r="S12" t="n">
+        <v>10</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Mörbylånga</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Öland</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Glömminge</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2024-10-14</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2024-10-14</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Patrik Celander</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Patrik Celander</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>120542163</v>
+      </c>
+      <c r="B13" t="n">
+        <v>100194</v>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Isgärde, Öl</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>594965</v>
+      </c>
+      <c r="R13" t="n">
+        <v>6290493</v>
+      </c>
+      <c r="S13" t="n">
+        <v>10</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Mörbylånga</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Öland</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Glömminge</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2024-10-14</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2024-10-14</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Patrik Celander</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Patrik Celander</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>120542171</v>
+      </c>
+      <c r="B14" t="n">
+        <v>91134</v>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>3884</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Hasselticka</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Dichomitus campestris</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>(Quél.) Domański &amp; Orlicz</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Isgärde, Öl</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>594893</v>
+      </c>
+      <c r="R14" t="n">
+        <v>6290513</v>
+      </c>
+      <c r="S14" t="n">
+        <v>10</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Mörbylånga</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Öland</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Glömminge</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2024-10-14</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2024-10-14</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Patrik Celander</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Patrik Celander</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>120542159</v>
+      </c>
+      <c r="B15" t="n">
+        <v>100194</v>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Isgärde, Öl</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>595218</v>
+      </c>
+      <c r="R15" t="n">
+        <v>6290436</v>
+      </c>
+      <c r="S15" t="n">
+        <v>10</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Mörbylånga</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Öland</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Glömminge</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2024-10-14</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2024-10-14</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Patrik Celander</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Patrik Celander</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>120542978</v>
+      </c>
+      <c r="B16" t="n">
+        <v>110061</v>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>219711</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Sårläka</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Sanicula europaea</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Isgärde, Öl</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>595255</v>
+      </c>
+      <c r="R16" t="n">
+        <v>6290434</v>
+      </c>
+      <c r="S16" t="n">
+        <v>10</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Mörbylånga</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Öland</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Glömminge</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2024-10-16</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2024-10-16</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Patrik Celander</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Patrik Celander, Örjan Fritz</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>120542980</v>
+      </c>
+      <c r="B17" t="n">
+        <v>90600</v>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>5442</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Tallticka</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Porodaedalea pini</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Isgärde, Öl</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>594945</v>
+      </c>
+      <c r="R17" t="n">
+        <v>6290509</v>
+      </c>
+      <c r="S17" t="n">
+        <v>10</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Mörbylånga</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Öland</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Glömminge</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2024-10-16</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2024-10-16</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Patrik Celander</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Patrik Celander, Örjan Fritz</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>120542160</v>
+      </c>
+      <c r="B18" t="n">
+        <v>100194</v>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Isgärde, Öl</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>595138</v>
+      </c>
+      <c r="R18" t="n">
+        <v>6290448</v>
+      </c>
+      <c r="S18" t="n">
+        <v>10</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Mörbylånga</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Öland</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Glömminge</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2024-10-14</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2024-10-14</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Patrik Celander</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Patrik Celander</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>120542153</v>
+      </c>
+      <c r="B19" t="n">
+        <v>100194</v>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Isgärde, Öl</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>594997</v>
+      </c>
+      <c r="R19" t="n">
+        <v>6290429</v>
+      </c>
+      <c r="S19" t="n">
+        <v>10</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Mörbylånga</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Öland</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Glömminge</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2024-10-14</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2024-10-14</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>Patrik Celander</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>Patrik Celander</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>120542158</v>
+      </c>
+      <c r="B20" t="n">
+        <v>100194</v>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Isgärde, Öl</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>595148</v>
+      </c>
+      <c r="R20" t="n">
+        <v>6290416</v>
+      </c>
+      <c r="S20" t="n">
+        <v>10</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Mörbylånga</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Öland</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Glömminge</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2024-10-14</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>2024-10-14</t>
+        </is>
+      </c>
+      <c r="AD20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>Patrik Celander</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>Patrik Celander</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>120542981</v>
+      </c>
+      <c r="B21" t="n">
+        <v>86365</v>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>448</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Mjölspindling</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Cortinarius flavovirens</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>Rob.Henry</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>Isgärde, Öl</t>
+        </is>
+      </c>
+      <c r="Q21" t="n">
+        <v>594894</v>
+      </c>
+      <c r="R21" t="n">
+        <v>6290515</v>
+      </c>
+      <c r="S21" t="n">
+        <v>10</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>Mörbylånga</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Öland</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Glömminge</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>2024-10-16</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>2024-10-16</t>
+        </is>
+      </c>
+      <c r="AD21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT21" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>Patrik Celander</t>
+        </is>
+      </c>
+      <c r="AX21" t="inlineStr">
+        <is>
+          <t>Patrik Celander, Örjan Fritz</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>120542162</v>
+      </c>
+      <c r="B22" t="n">
+        <v>100194</v>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>Isgärde, Öl</t>
+        </is>
+      </c>
+      <c r="Q22" t="n">
+        <v>595008</v>
+      </c>
+      <c r="R22" t="n">
+        <v>6290472</v>
+      </c>
+      <c r="S22" t="n">
+        <v>10</v>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>Mörbylånga</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>Öland</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>Glömminge</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>2024-10-14</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>2024-10-14</t>
+        </is>
+      </c>
+      <c r="AD22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT22" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>Patrik Celander</t>
+        </is>
+      </c>
+      <c r="AX22" t="inlineStr">
+        <is>
+          <t>Patrik Celander</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 21214-2023 artfynd.xlsx
+++ b/artfynd/A 21214-2023 artfynd.xlsx
@@ -1414,7 +1414,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>120542164</v>
+        <v>120542159</v>
       </c>
       <c r="B9" t="n">
         <v>100194</v>
@@ -1454,10 +1454,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>594894</v>
+        <v>595218</v>
       </c>
       <c r="R9" t="n">
-        <v>6290481</v>
+        <v>6290436</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1516,10 +1516,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>120542979</v>
+        <v>120542163</v>
       </c>
       <c r="B10" t="n">
-        <v>110061</v>
+        <v>100194</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1532,21 +1532,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>219711</v>
+        <v>222498</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Sårläka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Sanicula europaea</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1556,10 +1556,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>595162</v>
+        <v>594965</v>
       </c>
       <c r="R10" t="n">
-        <v>6290464</v>
+        <v>6290493</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1586,12 +1586,12 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2024-10-16</t>
+          <t>2024-10-14</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2024-10-16</t>
+          <t>2024-10-14</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1611,17 +1611,17 @@
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Patrik Celander, Örjan Fritz</t>
+          <t>Patrik Celander</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>120542154</v>
+        <v>120542981</v>
       </c>
       <c r="B11" t="n">
-        <v>8346</v>
+        <v>86365</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1630,25 +1630,25 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>106540</v>
+        <v>448</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Svart askbastborre</t>
+          <t>Mjölspindling</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Hylesinus crenatus</t>
+          <t>Cortinarius flavovirens</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Fabricius, 1787)</t>
+          <t>Rob.Henry</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1658,10 +1658,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>595044</v>
+        <v>594894</v>
       </c>
       <c r="R11" t="n">
-        <v>6290419</v>
+        <v>6290515</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1688,12 +1688,12 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2024-10-14</t>
+          <t>2024-10-16</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2024-10-14</t>
+          <t>2024-10-16</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1713,7 +1713,7 @@
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Patrik Celander</t>
+          <t>Patrik Celander, Örjan Fritz</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
@@ -1822,7 +1822,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>120542163</v>
+        <v>120542158</v>
       </c>
       <c r="B13" t="n">
         <v>100194</v>
@@ -1862,10 +1862,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>594965</v>
+        <v>595148</v>
       </c>
       <c r="R13" t="n">
-        <v>6290493</v>
+        <v>6290416</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2026,10 +2026,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>120542159</v>
+        <v>120542979</v>
       </c>
       <c r="B15" t="n">
-        <v>100194</v>
+        <v>110061</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2042,21 +2042,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>222498</v>
+        <v>219711</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Sårläka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Sanicula europaea</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2066,10 +2066,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>595218</v>
+        <v>595162</v>
       </c>
       <c r="R15" t="n">
-        <v>6290436</v>
+        <v>6290464</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2096,12 +2096,12 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2024-10-14</t>
+          <t>2024-10-16</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2024-10-14</t>
+          <t>2024-10-16</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2121,17 +2121,17 @@
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Patrik Celander</t>
+          <t>Patrik Celander, Örjan Fritz</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>120542978</v>
+        <v>120542153</v>
       </c>
       <c r="B16" t="n">
-        <v>110061</v>
+        <v>100194</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2144,21 +2144,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>219711</v>
+        <v>222498</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Sårläka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Sanicula europaea</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2168,10 +2168,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>595255</v>
+        <v>594997</v>
       </c>
       <c r="R16" t="n">
-        <v>6290434</v>
+        <v>6290429</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2198,12 +2198,12 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2024-10-16</t>
+          <t>2024-10-14</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2024-10-16</t>
+          <t>2024-10-14</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2223,17 +2223,17 @@
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Patrik Celander, Örjan Fritz</t>
+          <t>Patrik Celander</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>120542980</v>
+        <v>120542164</v>
       </c>
       <c r="B17" t="n">
-        <v>90600</v>
+        <v>100194</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2242,25 +2242,25 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>5442</v>
+        <v>222498</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2270,10 +2270,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>594945</v>
+        <v>594894</v>
       </c>
       <c r="R17" t="n">
-        <v>6290509</v>
+        <v>6290481</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2300,12 +2300,12 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2024-10-16</t>
+          <t>2024-10-14</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2024-10-16</t>
+          <t>2024-10-14</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2325,17 +2325,17 @@
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Patrik Celander, Örjan Fritz</t>
+          <t>Patrik Celander</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>120542160</v>
+        <v>120542980</v>
       </c>
       <c r="B18" t="n">
-        <v>100194</v>
+        <v>90600</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2344,25 +2344,25 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>222498</v>
+        <v>5442</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2372,10 +2372,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>595138</v>
+        <v>594945</v>
       </c>
       <c r="R18" t="n">
-        <v>6290448</v>
+        <v>6290509</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2402,12 +2402,12 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2024-10-14</t>
+          <t>2024-10-16</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2024-10-14</t>
+          <t>2024-10-16</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2427,17 +2427,17 @@
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Patrik Celander</t>
+          <t>Patrik Celander, Örjan Fritz</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>120542153</v>
+        <v>120542154</v>
       </c>
       <c r="B19" t="n">
-        <v>100194</v>
+        <v>8346</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2446,25 +2446,25 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>222498</v>
+        <v>106540</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Svart askbastborre</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Hylesinus crenatus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Fabricius, 1787)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2474,10 +2474,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>594997</v>
+        <v>595044</v>
       </c>
       <c r="R19" t="n">
-        <v>6290429</v>
+        <v>6290419</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2536,7 +2536,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>120542158</v>
+        <v>120542162</v>
       </c>
       <c r="B20" t="n">
         <v>100194</v>
@@ -2576,10 +2576,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>595148</v>
+        <v>595008</v>
       </c>
       <c r="R20" t="n">
-        <v>6290416</v>
+        <v>6290472</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2638,10 +2638,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>120542981</v>
+        <v>120542978</v>
       </c>
       <c r="B21" t="n">
-        <v>86365</v>
+        <v>110061</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2650,25 +2650,25 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>448</v>
+        <v>219711</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Mjölspindling</t>
+          <t>Sårläka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Cortinarius flavovirens</t>
+          <t>Sanicula europaea</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>Rob.Henry</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2678,10 +2678,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>594894</v>
+        <v>595255</v>
       </c>
       <c r="R21" t="n">
-        <v>6290515</v>
+        <v>6290434</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2740,7 +2740,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>120542162</v>
+        <v>120542160</v>
       </c>
       <c r="B22" t="n">
         <v>100194</v>
@@ -2780,10 +2780,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>595008</v>
+        <v>595138</v>
       </c>
       <c r="R22" t="n">
-        <v>6290472</v>
+        <v>6290448</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>

--- a/artfynd/A 21214-2023 artfynd.xlsx
+++ b/artfynd/A 21214-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY38"/>
+  <dimension ref="A1:AZ38"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -769,6 +774,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120542150</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -866,6 +876,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120542981</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -963,6 +978,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120542157</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1065,6 +1085,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115968055</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1162,6 +1187,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120542171</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1264,6 +1294,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/116267750</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1361,6 +1396,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120542980</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1463,6 +1503,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115864571</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1565,6 +1610,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115968058</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1667,6 +1717,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115968064</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1764,6 +1819,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120542154</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1866,6 +1926,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115864599</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -1963,6 +2028,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120542161</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2069,6 +2139,11 @@
           <t>Inventering av Ölands kärlväxtflora.</t>
         </is>
       </c>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/77221003</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2166,6 +2241,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/116267490</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2272,6 +2352,11 @@
           <t>Inventering av Ölands kärlväxtflora.</t>
         </is>
       </c>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/2223998</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2369,6 +2454,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120542978</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2466,6 +2556,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120542979</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2567,6 +2662,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127736601</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2668,6 +2768,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127736731</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2765,6 +2870,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127736732</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -2862,6 +2972,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127736764</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -2959,6 +3074,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115968056</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3056,6 +3176,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120542132</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3153,6 +3278,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120542143</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3250,6 +3380,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120542151</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3347,6 +3482,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120542153</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3444,6 +3584,11 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120542156</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3541,6 +3686,11 @@
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120542158</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -3638,6 +3788,11 @@
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120542159</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -3735,6 +3890,11 @@
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120542160</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -3832,6 +3992,11 @@
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120542162</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -3929,6 +4094,11 @@
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120542163</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -4026,6 +4196,11 @@
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120542164</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -4123,6 +4298,11 @@
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120542165</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -4220,6 +4400,11 @@
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127736762</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -4317,8 +4502,52 @@
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127736793</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>